--- a/AAII_Financials/Yearly/AMRX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMRX_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/AMRX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMRX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>AMRX</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2393600</v>
+      </c>
+      <c r="E8" s="3">
         <v>2212300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2093700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1992500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1626400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1663000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>775800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>824400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>860500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>596000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>511500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>581700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>512900</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1536900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1416500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1302000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1329600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1147200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>937600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>632000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>975500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>500800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>280500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>299000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>299100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>254600</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>856700</v>
+      </c>
+      <c r="E10" s="3">
         <v>795800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>791700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>663000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>479200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>725400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>143800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-151100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>359700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>315600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>212500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>282600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>258300</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,50 +873,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>164000</v>
+      </c>
+      <c r="E12" s="3">
         <v>195700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>201800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>179900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>188000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>194200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>80800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>80500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>70600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>79100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>68100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>160100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>82700</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -944,51 +960,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>70500</v>
+      </c>
+      <c r="E14" s="3">
         <v>294200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>63700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>54400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>35800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>326800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>281600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>60800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>35200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>8200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>30500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>14200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>9800</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2189200</v>
+      </c>
+      <c r="E17" s="3">
         <v>2307200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1941000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1901200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1674900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1705300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1179700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1318600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>807800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>507200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>517900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>498700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>415600</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>204400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-94900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>152700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>91300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-48500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-42300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-403900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-494200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>52700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>88800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>83000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>97300</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="E20" s="3">
         <v>5200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>15000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>18900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-16900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-40700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>34000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>153700</v>
-      </c>
-      <c r="N20" s="3">
-        <v>1000</v>
       </c>
       <c r="O20" s="3">
         <v>1000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>399800</v>
+      </c>
+      <c r="E21" s="3">
         <v>150400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>401100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>345600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>155200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>78300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-288100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-446500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>155300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>124600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>183400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>161900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>114000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>210600</v>
+      </c>
+      <c r="E22" s="3">
         <v>158400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>136300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>146000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>168200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>143600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>53400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>41400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>27300</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>200</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-40300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-248100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>31400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-35800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-220200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-202700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-451000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-576300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>59400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>90600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>146900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>83300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>98100</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E24" s="3">
         <v>6700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>11200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>383300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>18700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-104300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>20400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>33200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>45700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>27400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>32600</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-48700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-254800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>20200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-41400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-603600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-201500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-469700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-472000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>39000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>57400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>101300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>55900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>65500</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-84000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-130000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>10600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-18900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-361900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-21100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-469700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-472000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>39000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>57400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>101300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>55900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>65600</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1535,20 +1595,20 @@
       <c r="E29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G29" s="3">
         <v>110000</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="H29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>200</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>400</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>24</v>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-15000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-18900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>16900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>40700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-34000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-153700</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-1000</v>
       </c>
       <c r="O32" s="3">
         <v>-1000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-84000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-130000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>91100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-361900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-20900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-469300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-472000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>39000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>57400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>101300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>55900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>65600</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-84000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-130000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>91100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-361900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-20900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-469300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-472000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>39000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>57400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>101300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>55900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>65600</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,50 +1986,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>91500</v>
+      </c>
+      <c r="E41" s="3">
         <v>26000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>247800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>341400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>151200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>213400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>181800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>180100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>340400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>214900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>184600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>142200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>104400</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1973,188 +2062,203 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>200000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>228500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>156800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>242000</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>645700</v>
+      </c>
+      <c r="E43" s="3">
         <v>796900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>727700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>674200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>635900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>528900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>302000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>257400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>324500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>137600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>113000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>92200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>153800</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>581400</v>
+      </c>
+      <c r="E44" s="3">
         <v>530700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>489400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>490600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>381100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>457200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>158500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>175200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>125600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>80600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>70100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>89800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>54200</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>59300</v>
+      </c>
+      <c r="E45" s="3">
         <v>58200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>55200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>45300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>42100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>87100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>53400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>18400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>31700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>88500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>63500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>64600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>47000</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1377900</v>
+      </c>
+      <c r="E46" s="3">
         <v>1411800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1520100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1551500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1210200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1286600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>695600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>631100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>822100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>675600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>659700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>545500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>599900</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2194,93 +2298,102 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>550100</v>
+      </c>
+      <c r="E48" s="3">
         <v>589400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>639000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>605200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>620200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>544100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>124800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>233400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>214200</v>
-      </c>
-      <c r="L48" s="3">
-        <v>188200</v>
       </c>
       <c r="M48" s="3">
         <v>188200</v>
       </c>
       <c r="N48" s="3">
+        <v>188200</v>
+      </c>
+      <c r="O48" s="3">
         <v>180800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>118200</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1489100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1694900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1759900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1827400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1802300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2081200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>469800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>827800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>812200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>37500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>57200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>75500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>29800</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>55500</v>
+      </c>
+      <c r="E52" s="3">
         <v>103200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>20600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>33300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>440800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>61100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>130700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>74100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>161100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>125700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>62100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>53400</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3472600</v>
+      </c>
+      <c r="E54" s="3">
         <v>3799300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3939700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4006000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3665900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4352700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1351300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1823000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1922500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1079200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>996900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>864000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>793900</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,76 +2654,80 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>143600</v>
+      </c>
+      <c r="E57" s="3">
         <v>166000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>189100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>151100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>102000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>114800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>81100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>59000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>56300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>32000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>26800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>41300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>23000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>215600</v>
+      </c>
+      <c r="E58" s="3">
         <v>93400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>33700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>48400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>23500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>21700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>17800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>17700</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>24</v>
@@ -2608,123 +2741,132 @@
       <c r="O58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>487400</v>
+      </c>
+      <c r="E59" s="3">
         <v>493400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>454400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>477400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>424900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>417300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>255300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>244700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>270400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>126700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>126800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>104000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>202900</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>846600</v>
+      </c>
+      <c r="E60" s="3">
         <v>752800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>677200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>676900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>550400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>553900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>354200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>321300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>326800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>158700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>153900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>145300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>156900</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2486000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2692500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2778300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2834200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2674500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2669700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>769500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>813500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>424600</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2734,51 +2876,57 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>78700</v>
+      </c>
+      <c r="E62" s="3">
         <v>145200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>100200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>138200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>94200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>232800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>40300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>64200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>108700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>32600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>32800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>27600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>34100</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3452800</v>
+      </c>
+      <c r="E66" s="3">
         <v>3500900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3579300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3702800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3433900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3848000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1164100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1199000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>860100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>191300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>186700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>172900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>190900</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-490200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-406200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-276200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-286800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-377900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-20900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-372400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>98200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>570200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>531200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>473900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>372600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>316700</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E76" s="3">
         <v>298400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>360300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>303300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>232000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>504800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>187200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>624000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1062400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>887900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>810200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>691100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>602900</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-84000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-130000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>91100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-361900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-20900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-469300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-472000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>39000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>57400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>101300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>55900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>65600</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>229400</v>
+      </c>
+      <c r="E83" s="3">
         <v>240200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>233400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>235400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>207200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>137400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>109400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>88300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>68600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>34000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>36000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>77900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>15700</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>345600</v>
+      </c>
+      <c r="E89" s="3">
         <v>65100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>241800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>379000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>250200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>84200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>83900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>92500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>32800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>149900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>105800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6100</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-46800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-48800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-50900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-61800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-47200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-83100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-26700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-49400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-25200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-29900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-32800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-66900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-30500</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-69200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-174300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-194200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-317500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-19600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-396400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-627100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-467500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-16600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-115900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-85800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-15000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,8 +4220,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4006,11 +4239,11 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>-183000</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -4029,9 +4262,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-212600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-106600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-138100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>131800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-45800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>287700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-73700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>382500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>500900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>14400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>9000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>17300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>21300</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>200</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>63900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-221500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-90400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>194300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-66000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>140900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-160200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>125500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>30300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>42500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>37700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>12600</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/AMRX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMRX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>AMRX</t>
   </si>
@@ -744,7 +744,7 @@
         <v>1663000</v>
       </c>
       <c r="J8" s="3">
-        <v>775800</v>
+        <v>1033700</v>
       </c>
       <c r="K8" s="3">
         <v>824400</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1536900</v>
+        <v>1529700</v>
       </c>
       <c r="E9" s="3">
-        <v>1416500</v>
+        <v>1420800</v>
       </c>
       <c r="F9" s="3">
-        <v>1302000</v>
+        <v>1309700</v>
       </c>
       <c r="G9" s="3">
-        <v>1329600</v>
+        <v>1340200</v>
       </c>
       <c r="H9" s="3">
-        <v>1147200</v>
+        <v>1161500</v>
       </c>
       <c r="I9" s="3">
-        <v>937600</v>
+        <v>955000</v>
       </c>
       <c r="J9" s="3">
-        <v>632000</v>
+        <v>528000</v>
       </c>
       <c r="K9" s="3">
         <v>975500</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>856700</v>
+        <v>863900</v>
       </c>
       <c r="E10" s="3">
-        <v>795800</v>
+        <v>791500</v>
       </c>
       <c r="F10" s="3">
-        <v>791700</v>
+        <v>783900</v>
       </c>
       <c r="G10" s="3">
-        <v>663000</v>
+        <v>652300</v>
       </c>
       <c r="H10" s="3">
-        <v>479200</v>
+        <v>464900</v>
       </c>
       <c r="I10" s="3">
-        <v>725400</v>
+        <v>708000</v>
       </c>
       <c r="J10" s="3">
-        <v>143800</v>
+        <v>505700</v>
       </c>
       <c r="K10" s="3">
         <v>-151100</v>
@@ -898,7 +898,7 @@
         <v>194200</v>
       </c>
       <c r="J12" s="3">
-        <v>80800</v>
+        <v>171400</v>
       </c>
       <c r="K12" s="3">
         <v>80500</v>
@@ -970,25 +970,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>70500</v>
+        <v>107800</v>
       </c>
       <c r="E14" s="3">
-        <v>294200</v>
+        <v>295300</v>
       </c>
       <c r="F14" s="3">
-        <v>63700</v>
+        <v>63900</v>
       </c>
       <c r="G14" s="3">
         <v>54400</v>
       </c>
       <c r="H14" s="3">
-        <v>35800</v>
+        <v>228700</v>
       </c>
       <c r="I14" s="3">
-        <v>326800</v>
+        <v>327800</v>
       </c>
       <c r="J14" s="3">
-        <v>281600</v>
+        <v>11900</v>
       </c>
       <c r="K14" s="3">
         <v>60800</v>
@@ -1015,25 +1015,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>229400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>240200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>233400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>235400</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>243600</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>147800</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>45900</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>2189200</v>
+        <v>2122200</v>
       </c>
       <c r="E17" s="3">
-        <v>2307200</v>
+        <v>2012300</v>
       </c>
       <c r="F17" s="3">
-        <v>1941000</v>
+        <v>1877100</v>
       </c>
       <c r="G17" s="3">
-        <v>1901200</v>
+        <v>1846900</v>
       </c>
       <c r="H17" s="3">
-        <v>1674900</v>
+        <v>1639100</v>
       </c>
       <c r="I17" s="3">
-        <v>1705300</v>
+        <v>1377100</v>
       </c>
       <c r="J17" s="3">
-        <v>1179700</v>
+        <v>808500</v>
       </c>
       <c r="K17" s="3">
         <v>1318600</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>204400</v>
+        <v>271400</v>
       </c>
       <c r="E18" s="3">
-        <v>-94900</v>
+        <v>200000</v>
       </c>
       <c r="F18" s="3">
-        <v>152700</v>
+        <v>216600</v>
       </c>
       <c r="G18" s="3">
-        <v>91300</v>
+        <v>145700</v>
       </c>
       <c r="H18" s="3">
-        <v>-48500</v>
+        <v>-12700</v>
       </c>
       <c r="I18" s="3">
-        <v>-42300</v>
+        <v>285900</v>
       </c>
       <c r="J18" s="3">
-        <v>-403900</v>
+        <v>225200</v>
       </c>
       <c r="K18" s="3">
         <v>-494200</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-34000</v>
+        <v>-6800</v>
       </c>
       <c r="E20" s="3">
-        <v>5200</v>
+        <v>-5500</v>
       </c>
       <c r="F20" s="3">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="G20" s="3">
-        <v>18900</v>
+        <v>-18900</v>
       </c>
       <c r="H20" s="3">
-        <v>-3500</v>
+        <v>-189400</v>
       </c>
       <c r="I20" s="3">
-        <v>-16900</v>
+        <v>17300</v>
       </c>
       <c r="J20" s="3">
-        <v>6400</v>
+        <v>-29000</v>
       </c>
       <c r="K20" s="3">
         <v>-40700</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>399800</v>
+        <v>507600</v>
       </c>
       <c r="E21" s="3">
-        <v>150400</v>
+        <v>445700</v>
       </c>
       <c r="F21" s="3">
-        <v>401100</v>
+        <v>465000</v>
       </c>
       <c r="G21" s="3">
-        <v>345600</v>
+        <v>400000</v>
       </c>
       <c r="H21" s="3">
-        <v>155200</v>
+        <v>420300</v>
       </c>
       <c r="I21" s="3">
-        <v>78300</v>
+        <v>416500</v>
       </c>
       <c r="J21" s="3">
-        <v>-288100</v>
+        <v>300200</v>
       </c>
       <c r="K21" s="3">
         <v>-446500</v>
@@ -1293,7 +1293,7 @@
         <v>143600</v>
       </c>
       <c r="J22" s="3">
-        <v>53400</v>
+        <v>71100</v>
       </c>
       <c r="K22" s="3">
         <v>41400</v>
@@ -1338,7 +1338,7 @@
         <v>-202700</v>
       </c>
       <c r="J23" s="3">
-        <v>-451000</v>
+        <v>171300</v>
       </c>
       <c r="K23" s="3">
         <v>-576300</v>
@@ -1374,16 +1374,16 @@
         <v>11200</v>
       </c>
       <c r="G24" s="3">
-        <v>5600</v>
+        <v>-104400</v>
       </c>
       <c r="H24" s="3">
         <v>383300</v>
       </c>
       <c r="I24" s="3">
-        <v>-1200</v>
+        <v>-1400</v>
       </c>
       <c r="J24" s="3">
-        <v>18700</v>
+        <v>2000</v>
       </c>
       <c r="K24" s="3">
         <v>-104300</v>
@@ -1464,16 +1464,16 @@
         <v>20200</v>
       </c>
       <c r="G26" s="3">
-        <v>-41400</v>
+        <v>68600</v>
       </c>
       <c r="H26" s="3">
         <v>-603600</v>
       </c>
       <c r="I26" s="3">
-        <v>-201500</v>
+        <v>-201300</v>
       </c>
       <c r="J26" s="3">
-        <v>-469700</v>
+        <v>169300</v>
       </c>
       <c r="K26" s="3">
         <v>-472000</v>
@@ -1509,16 +1509,16 @@
         <v>10600</v>
       </c>
       <c r="G27" s="3">
-        <v>-18900</v>
+        <v>91100</v>
       </c>
       <c r="H27" s="3">
         <v>-361900</v>
       </c>
       <c r="I27" s="3">
-        <v>-21100</v>
+        <v>-20900</v>
       </c>
       <c r="J27" s="3">
-        <v>-469700</v>
+        <v>167700</v>
       </c>
       <c r="K27" s="3">
         <v>-472000</v>
@@ -1589,26 +1589,26 @@
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>24</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>110000</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>24</v>
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>24</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>34000</v>
+        <v>6800</v>
       </c>
       <c r="E32" s="3">
-        <v>-5200</v>
+        <v>5500</v>
       </c>
       <c r="F32" s="3">
-        <v>-15000</v>
+        <v>15000</v>
       </c>
       <c r="G32" s="3">
-        <v>-18900</v>
+        <v>18900</v>
       </c>
       <c r="H32" s="3">
-        <v>3500</v>
+        <v>189400</v>
       </c>
       <c r="I32" s="3">
-        <v>16900</v>
+        <v>-17300</v>
       </c>
       <c r="J32" s="3">
-        <v>-6400</v>
+        <v>29000</v>
       </c>
       <c r="K32" s="3">
         <v>40700</v>
@@ -1785,10 +1785,10 @@
         <v>-361900</v>
       </c>
       <c r="I33" s="3">
-        <v>-20900</v>
+        <v>-169700</v>
       </c>
       <c r="J33" s="3">
-        <v>-469300</v>
+        <v>167600</v>
       </c>
       <c r="K33" s="3">
         <v>-472000</v>
@@ -1875,10 +1875,10 @@
         <v>-361900</v>
       </c>
       <c r="I35" s="3">
-        <v>-20900</v>
+        <v>-169700</v>
       </c>
       <c r="J35" s="3">
-        <v>-469300</v>
+        <v>167600</v>
       </c>
       <c r="K35" s="3">
         <v>-472000</v>
@@ -2011,7 +2011,7 @@
         <v>213400</v>
       </c>
       <c r="J41" s="3">
-        <v>181800</v>
+        <v>74200</v>
       </c>
       <c r="K41" s="3">
         <v>180100</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2086,22 +2086,22 @@
         <v>645700</v>
       </c>
       <c r="E43" s="3">
-        <v>796900</v>
+        <v>796400</v>
       </c>
       <c r="F43" s="3">
-        <v>727700</v>
+        <v>694600</v>
       </c>
       <c r="G43" s="3">
-        <v>674200</v>
+        <v>668200</v>
       </c>
       <c r="H43" s="3">
         <v>635900</v>
       </c>
       <c r="I43" s="3">
-        <v>528900</v>
+        <v>565300</v>
       </c>
       <c r="J43" s="3">
-        <v>302000</v>
+        <v>382700</v>
       </c>
       <c r="K43" s="3">
         <v>257400</v>
@@ -2146,7 +2146,7 @@
         <v>457200</v>
       </c>
       <c r="J44" s="3">
-        <v>158500</v>
+        <v>284000</v>
       </c>
       <c r="K44" s="3">
         <v>175200</v>
@@ -2172,26 +2172,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>59300</v>
+      <c r="D45" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E45" s="3">
-        <v>58200</v>
+        <v>500</v>
       </c>
       <c r="F45" s="3">
-        <v>55200</v>
+        <v>33100</v>
       </c>
       <c r="G45" s="3">
-        <v>45300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>42100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>87100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>53400</v>
+        <v>6000</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K45" s="3">
         <v>18400</v>
@@ -2236,7 +2236,7 @@
         <v>1286600</v>
       </c>
       <c r="J46" s="3">
-        <v>695600</v>
+        <v>771900</v>
       </c>
       <c r="K46" s="3">
         <v>631100</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>37100</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
+        <v>85600</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>16400</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2317,16 +2317,16 @@
         <v>639000</v>
       </c>
       <c r="G48" s="3">
-        <v>605200</v>
+        <v>604700</v>
       </c>
       <c r="H48" s="3">
-        <v>620200</v>
+        <v>620600</v>
       </c>
       <c r="I48" s="3">
         <v>544100</v>
       </c>
       <c r="J48" s="3">
-        <v>124800</v>
+        <v>486800</v>
       </c>
       <c r="K48" s="3">
         <v>233400</v>
@@ -2371,7 +2371,7 @@
         <v>2081200</v>
       </c>
       <c r="J49" s="3">
-        <v>469800</v>
+        <v>71000</v>
       </c>
       <c r="K49" s="3">
         <v>827800</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>55500</v>
+        <v>14000</v>
       </c>
       <c r="E52" s="3">
-        <v>103200</v>
+        <v>15400</v>
       </c>
       <c r="F52" s="3">
-        <v>20600</v>
+        <v>19000</v>
       </c>
       <c r="G52" s="3">
-        <v>21900</v>
+        <v>19700</v>
       </c>
       <c r="H52" s="3">
-        <v>33300</v>
+        <v>13400</v>
       </c>
       <c r="I52" s="3">
-        <v>440800</v>
+        <v>63600</v>
       </c>
       <c r="J52" s="3">
-        <v>61100</v>
+        <v>11300</v>
       </c>
       <c r="K52" s="3">
         <v>130700</v>
@@ -2596,7 +2596,7 @@
         <v>4352700</v>
       </c>
       <c r="J54" s="3">
-        <v>1351300</v>
+        <v>1341900</v>
       </c>
       <c r="K54" s="3">
         <v>1823000</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>143600</v>
+        <v>145500</v>
       </c>
       <c r="E57" s="3">
-        <v>166000</v>
+        <v>166800</v>
       </c>
       <c r="F57" s="3">
-        <v>189100</v>
+        <v>132900</v>
       </c>
       <c r="G57" s="3">
-        <v>151100</v>
+        <v>154100</v>
       </c>
       <c r="H57" s="3">
-        <v>102000</v>
+        <v>103000</v>
       </c>
       <c r="I57" s="3">
         <v>114800</v>
       </c>
       <c r="J57" s="3">
-        <v>81100</v>
+        <v>70000</v>
       </c>
       <c r="K57" s="3">
         <v>59000</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>215600</v>
+        <v>227600</v>
       </c>
       <c r="E58" s="3">
-        <v>93400</v>
+        <v>104600</v>
       </c>
       <c r="F58" s="3">
-        <v>33700</v>
+        <v>46000</v>
       </c>
       <c r="G58" s="3">
-        <v>48400</v>
+        <v>57500</v>
       </c>
       <c r="H58" s="3">
-        <v>23500</v>
+        <v>37000</v>
       </c>
       <c r="I58" s="3">
         <v>21700</v>
       </c>
       <c r="J58" s="3">
-        <v>17800</v>
+        <v>89500</v>
       </c>
       <c r="K58" s="3">
         <v>17700</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>487400</v>
+        <v>227400</v>
       </c>
       <c r="E59" s="3">
-        <v>493400</v>
+        <v>263100</v>
       </c>
       <c r="F59" s="3">
-        <v>454400</v>
+        <v>277800</v>
       </c>
       <c r="G59" s="3">
-        <v>477400</v>
+        <v>207300</v>
       </c>
       <c r="H59" s="3">
-        <v>424900</v>
+        <v>176300</v>
       </c>
       <c r="I59" s="3">
-        <v>417300</v>
+        <v>200800</v>
       </c>
       <c r="J59" s="3">
-        <v>255300</v>
+        <v>72200</v>
       </c>
       <c r="K59" s="3">
         <v>244700</v>
@@ -2814,7 +2814,7 @@
         <v>553900</v>
       </c>
       <c r="J60" s="3">
-        <v>354200</v>
+        <v>296900</v>
       </c>
       <c r="K60" s="3">
         <v>321300</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2486000</v>
+        <v>2522900</v>
       </c>
       <c r="E61" s="3">
-        <v>2692500</v>
+        <v>2740500</v>
       </c>
       <c r="F61" s="3">
-        <v>2778300</v>
+        <v>2841500</v>
       </c>
       <c r="G61" s="3">
-        <v>2834200</v>
+        <v>2941300</v>
       </c>
       <c r="H61" s="3">
-        <v>2674500</v>
+        <v>2733000</v>
       </c>
       <c r="I61" s="3">
         <v>2669700</v>
       </c>
       <c r="J61" s="3">
-        <v>769500</v>
+        <v>1395300</v>
       </c>
       <c r="K61" s="3">
         <v>813500</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>78700</v>
+        <v>41800</v>
       </c>
       <c r="E62" s="3">
-        <v>145200</v>
+        <v>97100</v>
       </c>
       <c r="F62" s="3">
-        <v>100200</v>
+        <v>37000</v>
       </c>
       <c r="G62" s="3">
-        <v>138200</v>
+        <v>31000</v>
       </c>
       <c r="H62" s="3">
-        <v>94200</v>
+        <v>35700</v>
       </c>
       <c r="I62" s="3">
-        <v>232800</v>
+        <v>231700</v>
       </c>
       <c r="J62" s="3">
-        <v>40300</v>
+        <v>22800</v>
       </c>
       <c r="K62" s="3">
         <v>64200</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3452800</v>
+        <v>3411300</v>
       </c>
       <c r="E66" s="3">
-        <v>3500900</v>
+        <v>3590400</v>
       </c>
       <c r="F66" s="3">
-        <v>3579300</v>
+        <v>3555800</v>
       </c>
       <c r="G66" s="3">
-        <v>3702800</v>
+        <v>3649300</v>
       </c>
       <c r="H66" s="3">
-        <v>3433900</v>
+        <v>3319100</v>
       </c>
       <c r="I66" s="3">
-        <v>3848000</v>
+        <v>3456400</v>
       </c>
       <c r="J66" s="3">
-        <v>1164100</v>
+        <v>1717500</v>
       </c>
       <c r="K66" s="3">
         <v>1199000</v>
@@ -3328,7 +3328,7 @@
         <v>-20900</v>
       </c>
       <c r="J72" s="3">
-        <v>-372400</v>
+        <v>-382800</v>
       </c>
       <c r="K72" s="3">
         <v>98200</v>
@@ -3508,7 +3508,7 @@
         <v>504800</v>
       </c>
       <c r="J76" s="3">
-        <v>187200</v>
+        <v>-385700</v>
       </c>
       <c r="K76" s="3">
         <v>624000</v>
@@ -3645,10 +3645,10 @@
         <v>-361900</v>
       </c>
       <c r="I81" s="3">
-        <v>-20900</v>
+        <v>-169700</v>
       </c>
       <c r="J81" s="3">
-        <v>-469300</v>
+        <v>167600</v>
       </c>
       <c r="K81" s="3">
         <v>-472000</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>229400</v>
+        <v>66200</v>
       </c>
       <c r="E83" s="3">
-        <v>240200</v>
+        <v>68100</v>
       </c>
       <c r="F83" s="3">
-        <v>233400</v>
+        <v>60700</v>
       </c>
       <c r="G83" s="3">
-        <v>235400</v>
+        <v>60400</v>
       </c>
       <c r="H83" s="3">
-        <v>207200</v>
+        <v>63300</v>
       </c>
       <c r="I83" s="3">
-        <v>137400</v>
+        <v>64400</v>
       </c>
       <c r="J83" s="3">
-        <v>109400</v>
+        <v>42000</v>
       </c>
       <c r="K83" s="3">
         <v>88300</v>
@@ -3982,7 +3982,7 @@
         <v>250200</v>
       </c>
       <c r="J89" s="3">
-        <v>84200</v>
+        <v>234200</v>
       </c>
       <c r="K89" s="3">
         <v>83900</v>
@@ -4046,7 +4046,7 @@
         <v>-83100</v>
       </c>
       <c r="J91" s="3">
-        <v>-26700</v>
+        <v>-94800</v>
       </c>
       <c r="K91" s="3">
         <v>-49400</v>
@@ -4181,7 +4181,7 @@
         <v>-396400</v>
       </c>
       <c r="J94" s="3">
-        <v>-9700</v>
+        <v>-98600</v>
       </c>
       <c r="K94" s="3">
         <v>-627100</v>
@@ -4242,10 +4242,10 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-183000</v>
+        <v>183000</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>375300</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4425,7 +4425,7 @@
         <v>287700</v>
       </c>
       <c r="J100" s="3">
-        <v>-73700</v>
+        <v>-95000</v>
       </c>
       <c r="K100" s="3">
         <v>382500</v>
@@ -4470,7 +4470,7 @@
         <v>-700</v>
       </c>
       <c r="J101" s="3">
-        <v>800</v>
+        <v>-200</v>
       </c>
       <c r="K101" s="3">
         <v>500</v>
@@ -4515,7 +4515,7 @@
         <v>140900</v>
       </c>
       <c r="J102" s="3">
-        <v>1600</v>
+        <v>40400</v>
       </c>
       <c r="K102" s="3">
         <v>-160200</v>

--- a/AAII_Financials/Yearly/AMRX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMRX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t>AMRX</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2794000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2393600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2212300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2093700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1992500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1626400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1663000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1033700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>824400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>860500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>596000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>511500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>581700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>512900</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1778400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1529700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1420800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1309700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1340200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1161500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>955000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>528000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>975500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>500800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>280500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>299000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>299100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>254600</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1015500</v>
+      </c>
+      <c r="E10" s="3">
         <v>863900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>791500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>783900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>652300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>464900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>708000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>505700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-151100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>359700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>315600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>212500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>282600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>258300</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,53 +886,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>190700</v>
+      </c>
+      <c r="E12" s="3">
         <v>164000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>195700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>201800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>179900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>188000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>194200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>171400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>80500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>70600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>79100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>68100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>160100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>82700</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -963,81 +979,87 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>95300</v>
+      </c>
+      <c r="E14" s="3">
         <v>107800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>295300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>63900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>54400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>228700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>327800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>60800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>35200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>8200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>30500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>14200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>9800</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>236200</v>
+      </c>
+      <c r="E15" s="3">
         <v>229400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>240200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>233400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>235400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>243600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>147800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>45900</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1053,9 +1075,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2445600</v>
+      </c>
+      <c r="E17" s="3">
         <v>2122200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2012300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1877100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1846900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1639100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1377100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>808500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1318600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>807800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>507200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>517900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>498700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>415600</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>348400</v>
+      </c>
+      <c r="E18" s="3">
         <v>271400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>200000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>216600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>145700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-12700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>285900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>225200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-494200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>52700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>88800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>83000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>97300</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>49500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-15000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-18900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-189400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>17300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-29000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-40700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>34000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>153700</v>
-      </c>
-      <c r="O20" s="3">
-        <v>1000</v>
       </c>
       <c r="P20" s="3">
         <v>1000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>535100</v>
+      </c>
+      <c r="E21" s="3">
         <v>507600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>445700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>465000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>400000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>420300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>416500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>300200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-446500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>155300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>124600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>183400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>161900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>114000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>258600</v>
+      </c>
+      <c r="E22" s="3">
         <v>210600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>158400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>136300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>146000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>168200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>143600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>71100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>41400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>27300</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>200</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-40300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-248100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>31400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-35800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-220200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-202700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>171300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-576300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>59400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>90600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>146900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>83300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>98100</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E24" s="3">
         <v>8500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>11200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-104400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>383300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-104300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>20400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>33200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>45700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>27400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>32600</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-73900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-48700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-254800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>20200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>68600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-603600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-201300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>169300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-472000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>39000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>57400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>101300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>55900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>65500</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-116900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-84000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-130000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>10600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>91100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-361900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-20900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>167700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-472000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>39000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>57400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>101300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>55900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>65600</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1610,8 +1670,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>24</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>24</v>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-49500</v>
+      </c>
+      <c r="E32" s="3">
         <v>6800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>15000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>18900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>189400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-17300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>29000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>40700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-34000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-153700</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-1000</v>
       </c>
       <c r="P32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-116900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-84000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-130000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>10600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>91100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-361900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-169700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>167600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-472000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>39000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>57400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>101300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>55900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>65600</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-116900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-84000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-130000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>10600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>91100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-361900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-169700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>167600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-472000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>39000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>57400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>101300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>55900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>65600</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,205 +2072,218 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>110600</v>
+      </c>
+      <c r="E41" s="3">
         <v>91500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>26000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>247800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>341400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>151200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>213400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>74200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>180100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>340400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>214900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>184600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>142200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>104400</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E42" s="3">
         <v>2200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1900</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>200000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>228500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>156800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>242000</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>808600</v>
+      </c>
+      <c r="E43" s="3">
         <v>645700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>796400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>694600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>668200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>635900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>565300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>382700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>257400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>324500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>137600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>113000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>92200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>153800</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>612500</v>
+      </c>
+      <c r="E44" s="3">
         <v>581400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>530700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>489400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>490600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>381100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>457200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>284000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>175200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>125600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>80600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>70100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>89800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>54200</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>33100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6000</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>24</v>
@@ -2193,98 +2291,104 @@
       <c r="J45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="3">
         <v>18400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>31700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>88500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>63500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>64600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>47000</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1587800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1377900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1411800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1520100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1551500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1210200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1286600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>771900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>631100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>822100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>675600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>659700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>545500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>599900</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E47" s="3">
         <v>37100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>85600</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" s="3">
         <v>16400</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2301,99 +2405,108 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>523700</v>
+      </c>
+      <c r="E48" s="3">
         <v>550100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>589400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>639000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>604700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>620600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>544100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>486800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>233400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>214200</v>
-      </c>
-      <c r="M48" s="3">
-        <v>188200</v>
       </c>
       <c r="N48" s="3">
         <v>188200</v>
       </c>
       <c r="O48" s="3">
+        <v>188200</v>
+      </c>
+      <c r="P48" s="3">
         <v>180800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>118200</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1329800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1489100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1694900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1759900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1827400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1802300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2081200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>71000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>827800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>812200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>37500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>57200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>75500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>29800</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E52" s="3">
         <v>14000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>15400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>19700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>63600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>130700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>74100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>161100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>125700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>62100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>53400</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3501400</v>
+      </c>
+      <c r="E54" s="3">
         <v>3472600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3799300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3939700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4006000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3665900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4352700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1341900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1823000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1922500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1079200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>996900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>864000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>793900</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,82 +2784,86 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>259800</v>
+      </c>
+      <c r="E57" s="3">
         <v>145500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>166800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>132900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>154100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>103000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>114800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>70000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>59000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>56300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>32000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>26800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>41300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>23000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>340300</v>
+      </c>
+      <c r="E58" s="3">
         <v>227600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>104600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>46000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>57500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>37000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>21700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>89500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>17700</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>24</v>
@@ -2744,132 +2877,141 @@
       <c r="P58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>222400</v>
+      </c>
+      <c r="E59" s="3">
         <v>227400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>263100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>277800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>207300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>176300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>200800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>72200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>244700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>270400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>126700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>126800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>104000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>202900</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1129800</v>
+      </c>
+      <c r="E60" s="3">
         <v>846600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>752800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>677200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>676900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>550400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>553900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>296900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>321300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>326800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>158700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>153900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>145300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>156900</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2252900</v>
+      </c>
+      <c r="E61" s="3">
         <v>2522900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2740500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2841500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2941300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2733000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2669700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1395300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>813500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>424600</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -2879,54 +3021,60 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>163300</v>
+      </c>
+      <c r="E62" s="3">
         <v>41800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>97100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>37000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>31000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>35700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>231700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>22800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>64200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>108700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>32600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>32800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>27600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>34100</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3546000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3411300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3590400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3555800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3649300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3319100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3456400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1717500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1199000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>860100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>191300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>186700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>172900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>190900</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-607100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-490200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-406200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-276200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-286800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-377900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-20900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-382800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>98200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>570200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>531200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>473900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>372600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>316700</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-109300</v>
+      </c>
+      <c r="E76" s="3">
         <v>19800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>298400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>360300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>303300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>232000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>504800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-385700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>624000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1062400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>887900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>810200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>691100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>602900</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-116900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-84000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-130000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>10600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>91100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-361900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-169700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>167600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-472000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>39000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>57400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>101300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>55900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>65600</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E83" s="3">
         <v>66200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>68100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>60700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>60400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>63300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>64400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>42000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>88300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>68600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>34000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>36000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>77900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>15700</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>295100</v>
+      </c>
+      <c r="E89" s="3">
         <v>345600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>65100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>241800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>379000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>250200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>234200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>83900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>92500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>32800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>149900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>105800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6100</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-60300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-46800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-48800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-50900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-61800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-47200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-83100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-94800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-49400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-25200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-29900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-32800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-66900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-30500</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-63000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-69200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-174300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-194200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-317500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-19600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-396400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-98600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-627100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-467500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-16600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-115900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-85800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,8 +4453,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4242,14 +4475,14 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>183000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>375300</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4265,9 +4498,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-211800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-212600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-106600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-138100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>131800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-45800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>287700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-95000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>382500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>500900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>14400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>9000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>17300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>21300</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-5700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E102" s="3">
         <v>63900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-221500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-90400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>194300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-66000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>140900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>40400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-160200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>125500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>30300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>42500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>37700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>12600</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/AMRX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMRX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
   <si>
     <t>AMRX</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3018800</v>
+      </c>
+      <c r="E8" s="3">
         <v>2794000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2393600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2212300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2093700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1992500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1626400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1663000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1033700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>824400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>860500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>596000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>511500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>581700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>512900</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1890300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1778400</v>
       </c>
-      <c r="E9" s="3">
-        <v>1529700</v>
-      </c>
       <c r="F9" s="3">
+        <v>1540700</v>
+      </c>
+      <c r="G9" s="3">
         <v>1420800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1309700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1340200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1161500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>955000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>528000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>975500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>500800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>280500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>299000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>299100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>254600</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1128500</v>
+      </c>
+      <c r="E10" s="3">
         <v>1015500</v>
       </c>
-      <c r="E10" s="3">
-        <v>863900</v>
-      </c>
       <c r="F10" s="3">
+        <v>852900</v>
+      </c>
+      <c r="G10" s="3">
         <v>791500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>783900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>652300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>464900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>708000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>505700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-151100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>359700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>315600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>212500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>282600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>258300</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,56 +899,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>190700</v>
+        <v>186200</v>
       </c>
       <c r="E12" s="3">
-        <v>164000</v>
+        <v>190600</v>
       </c>
       <c r="F12" s="3">
+        <v>163900</v>
+      </c>
+      <c r="G12" s="3">
         <v>195700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>201800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>179900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>188000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>194200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>171400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>80500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>70600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>79100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>68100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>160100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>82700</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -982,87 +998,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>95300</v>
+        <v>58000</v>
       </c>
       <c r="E14" s="3">
-        <v>107800</v>
+        <v>96200</v>
       </c>
       <c r="F14" s="3">
+        <v>111300</v>
+      </c>
+      <c r="G14" s="3">
         <v>295300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>63900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>54400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>228700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>327800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>11900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>60800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>35200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>8200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>30500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>14200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>9800</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>223600</v>
+      </c>
+      <c r="E15" s="3">
         <v>236200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>229400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>240200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>233400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>235400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>243600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>147800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>45900</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>2445600</v>
+        <v>2598100</v>
       </c>
       <c r="E17" s="3">
-        <v>2122200</v>
+        <v>2444700</v>
       </c>
       <c r="F17" s="3">
+        <v>2118700</v>
+      </c>
+      <c r="G17" s="3">
         <v>2012300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1877100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1846900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1639100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1377100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>808500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1318600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>807800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>507200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>517900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>498700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>415600</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>348400</v>
+        <v>420700</v>
       </c>
       <c r="E18" s="3">
-        <v>271400</v>
+        <v>349300</v>
       </c>
       <c r="F18" s="3">
+        <v>274900</v>
+      </c>
+      <c r="G18" s="3">
         <v>200000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>216600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>145700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-12700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>285900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>225200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-494200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>52700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>88800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>83000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>97300</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1212,248 +1244,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E20" s="3">
         <v>49500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-15000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-18900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-189400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>17300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-29000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-40700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>34000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>153700</v>
-      </c>
-      <c r="P20" s="3">
-        <v>1000</v>
       </c>
       <c r="Q20" s="3">
         <v>1000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>535100</v>
+        <v>661800</v>
       </c>
       <c r="E21" s="3">
-        <v>507600</v>
+        <v>536000</v>
       </c>
       <c r="F21" s="3">
+        <v>511100</v>
+      </c>
+      <c r="G21" s="3">
         <v>445700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>465000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>400000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>420300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>416500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>300200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-446500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>155300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>124600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>183400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>161900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>114000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>241100</v>
+      </c>
+      <c r="E22" s="3">
         <v>258600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>210600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>158400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>136300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>146000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>168200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>143600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>71100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>41400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>27300</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>139200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-55000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-40300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-248100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>31400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-35800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-220200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-202700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>171300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-576300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>59400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>90600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>146900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>83300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>98100</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E24" s="3">
         <v>18900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-104400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>383300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-104300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>20400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>33200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>45700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>27400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>32600</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>127900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-73900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-48700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-254800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>20200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>68600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-603600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-201300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>169300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-472000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>39000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>57400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>101300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>55900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>65500</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>72100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-116900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-84000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-130000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>91100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-361900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-20900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>167700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-472000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>39000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>57400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>101300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>55900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>65600</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1673,8 +1733,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>24</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>24</v>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-49500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>15000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>18900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>189400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-17300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>29000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>40700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-34000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-153700</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-1000</v>
       </c>
       <c r="Q32" s="3">
         <v>-1000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>72100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-116900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-84000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-130000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>91100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-361900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-169700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>167600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-472000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>39000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>57400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>101300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>55900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>65600</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>72100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-116900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-84000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-130000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>91100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-361900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-169700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>167600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-472000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>39000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>57400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>101300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>55900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>65600</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,200 +2158,213 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E41" s="3">
         <v>110600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>91500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>26000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>247800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>341400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>151200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>213400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>74200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>180100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>340400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>214900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>184600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>142200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>104400</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E42" s="3">
         <v>1900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1900</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>200000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>228500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>156800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>242000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>939900</v>
+      </c>
+      <c r="E43" s="3">
         <v>808600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>645700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>796400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>694600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>668200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>635900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>565300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>382700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>257400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>324500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>137600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>113000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>92200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>153800</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>606300</v>
+      </c>
+      <c r="E44" s="3">
         <v>612500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>581400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>530700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>489400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>490600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>381100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>457200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>284000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>175200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>125600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>80600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>70100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>89800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>54200</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2276,17 +2374,17 @@
       <c r="E45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>33100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6000</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>24</v>
@@ -2294,104 +2392,110 @@
       <c r="K45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M45" s="3">
         <v>18400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>31700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>88500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>63500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>64600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>47000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1911200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1587800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1377900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1411800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1520100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1551500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1210200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1286600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>771900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>631100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>822100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>675600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>659700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>545500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>599900</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E47" s="3">
         <v>35900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>37100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>85600</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" s="3">
         <v>16400</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2408,105 +2512,114 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>550300</v>
+      </c>
+      <c r="E48" s="3">
         <v>523700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>550100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>589400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>639000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>604700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>620600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>544100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>486800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>233400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>214200</v>
-      </c>
-      <c r="N48" s="3">
-        <v>188200</v>
       </c>
       <c r="O48" s="3">
         <v>188200</v>
       </c>
       <c r="P48" s="3">
+        <v>188200</v>
+      </c>
+      <c r="Q48" s="3">
         <v>180800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>118200</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1159000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1329800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1489100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1694900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1759900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1827400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1802300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2081200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>71000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>827800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>812200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>37500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>57200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>75500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>29800</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>46900</v>
+      </c>
+      <c r="E52" s="3">
         <v>21400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>14000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>19000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>19700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>63600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>130700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>74100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>161100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>125700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>62100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>53400</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3678300</v>
+      </c>
+      <c r="E54" s="3">
         <v>3501400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3472600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3799300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3939700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4006000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3665900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4352700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1341900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1823000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1922500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1079200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>996900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>864000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>793900</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,88 +2914,92 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>254900</v>
+      </c>
+      <c r="E57" s="3">
         <v>259800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>145500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>166800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>132900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>154100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>103000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>114800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>70000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>59000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>56300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>32000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>26800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>41300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>23000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E58" s="3">
         <v>340300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>227600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>104600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>46000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>57500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>37000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>21700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>89500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>17700</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>24</v>
@@ -2880,141 +3013,150 @@
       <c r="Q58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>222400</v>
+        <v>276500</v>
       </c>
       <c r="E59" s="3">
+        <v>212100</v>
+      </c>
+      <c r="F59" s="3">
         <v>227400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>263100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>277800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>207300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>176300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>200800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>72200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>244700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>270400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>126700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>126800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>104000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>202900</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>881600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1129800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>846600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>752800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>677200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>676900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>550400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>553900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>296900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>321300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>326800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>158700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>153900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>145300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>156900</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2667500</v>
+      </c>
+      <c r="E61" s="3">
         <v>2252900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2522900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2740500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2841500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2941300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2733000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2669700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1395300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>813500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>424600</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3024,57 +3166,63 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>123200</v>
+      </c>
+      <c r="E62" s="3">
         <v>163300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>41800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>97100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>37000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>31000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>35700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>231700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>22800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>64200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>108700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>32600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>32800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>27600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>34100</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3672300</v>
+      </c>
+      <c r="E66" s="3">
         <v>3546000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3411300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3590400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3555800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3649300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3319100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3456400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1717500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1199000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>860100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>191300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>186700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>172900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>190900</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-535000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-607100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-490200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-406200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-276200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-286800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-377900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-20900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-382800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>98200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>570200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>531200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>473900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>372600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>316700</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-70800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-109300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>19800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>298400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>360300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>303300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>232000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>504800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-385700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>624000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1062400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>887900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>810200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>691100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>602900</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>72100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-116900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-84000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-130000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>91100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-361900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-169700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>167600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-472000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>39000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>57400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>101300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>55900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>65600</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E83" s="3">
         <v>62600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>66200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>68100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>60700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>60400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>63300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>64400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>42000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>88300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>68600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>34000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>36000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>77900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>15700</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>340000</v>
+      </c>
+      <c r="E89" s="3">
         <v>295100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>345600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>65100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>241800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>379000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>250200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>234200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>83900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>92500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>32800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>149900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>105800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6100</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-98800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-60300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-46800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-48800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-50900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-61800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-47200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-83100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-94800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-49400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-25200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-29900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-32800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-66900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-30500</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-112300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-63000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-69200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-174300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-194200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-317500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-19600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-396400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-98600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-627100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-467500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-16600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-115900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-85800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-15000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,8 +4686,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4478,14 +4711,14 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>183000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>375300</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4501,9 +4734,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-31500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-211800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-212600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-106600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-138100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>131800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-45800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>287700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-95000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>382500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>500900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>14400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>9000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>17300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>21300</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-5700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>200</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>194500</v>
+      </c>
+      <c r="E102" s="3">
         <v>19300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>63900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-221500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-90400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>194300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-66000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>140900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>40400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-160200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>125500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>30300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>42500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>37700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>12600</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/AMRX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMRX_YR_FIN.xlsx
@@ -1011,10 +1011,10 @@
         <v>58000</v>
       </c>
       <c r="E14" s="3">
-        <v>96200</v>
+        <v>95300</v>
       </c>
       <c r="F14" s="3">
-        <v>111300</v>
+        <v>96800</v>
       </c>
       <c r="G14" s="3">
         <v>295300</v>
@@ -1131,10 +1131,10 @@
         <v>2598100</v>
       </c>
       <c r="E17" s="3">
-        <v>2444700</v>
+        <v>2445600</v>
       </c>
       <c r="F17" s="3">
-        <v>2118700</v>
+        <v>2133200</v>
       </c>
       <c r="G17" s="3">
         <v>2012300</v>
@@ -1182,10 +1182,10 @@
         <v>420700</v>
       </c>
       <c r="E18" s="3">
-        <v>349300</v>
+        <v>348400</v>
       </c>
       <c r="F18" s="3">
-        <v>274900</v>
+        <v>260400</v>
       </c>
       <c r="G18" s="3">
         <v>200000</v>
@@ -1305,10 +1305,10 @@
         <v>661800</v>
       </c>
       <c r="E21" s="3">
-        <v>536000</v>
+        <v>535100</v>
       </c>
       <c r="F21" s="3">
-        <v>511100</v>
+        <v>496600</v>
       </c>
       <c r="G21" s="3">
         <v>445700</v>
